--- a/24th June,2026 Task.xlsx
+++ b/24th June,2026 Task.xlsx
@@ -736,13 +736,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -782,9 +779,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -929,14 +923,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -945,7 +942,57 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Title" xfId="1" builtinId="15"/>
   </cellStyles>
-  <dxfs count="78">
+  <dxfs count="101">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C6500"/>
@@ -957,6 +1004,13 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -967,6 +1021,23 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -978,6 +1049,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1008,6 +1089,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1023,6 +1134,110 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2767,107 +2982,107 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:E21" totalsRowShown="0" headerRowDxfId="77" dataDxfId="75" headerRowBorderDxfId="76" tableBorderDxfId="74" totalsRowBorderDxfId="73">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:E21" totalsRowShown="0" headerRowDxfId="100" dataDxfId="98" headerRowBorderDxfId="99" tableBorderDxfId="97" totalsRowBorderDxfId="96">
   <autoFilter ref="A1:E21"/>
   <tableColumns count="5">
-    <tableColumn id="1" name="Employee ID" dataDxfId="72"/>
-    <tableColumn id="2" name="Name" dataDxfId="71"/>
-    <tableColumn id="3" name="Department" dataDxfId="70"/>
-    <tableColumn id="4" name="Salary" dataDxfId="69"/>
-    <tableColumn id="5" name="Joining Date" dataDxfId="68"/>
+    <tableColumn id="1" name="Employee ID" dataDxfId="95"/>
+    <tableColumn id="2" name="Name" dataDxfId="94"/>
+    <tableColumn id="3" name="Department" dataDxfId="93"/>
+    <tableColumn id="4" name="Salary" dataDxfId="92"/>
+    <tableColumn id="5" name="Joining Date" dataDxfId="91"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A2:D22" totalsRowShown="0" headerRowDxfId="67" dataDxfId="65" headerRowBorderDxfId="66" tableBorderDxfId="64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A2:D22" totalsRowShown="0" headerRowDxfId="90" dataDxfId="88" headerRowBorderDxfId="89" tableBorderDxfId="87">
   <autoFilter ref="A2:D22"/>
   <tableColumns count="4">
-    <tableColumn id="1" name="Product Name" dataDxfId="63" dataCellStyle="Hyperlink">
+    <tableColumn id="1" name="Product Name" dataDxfId="86" dataCellStyle="Hyperlink">
       <calculatedColumnFormula>CHOOSE(RANDBETWEEN(1, 4), "Laptop Dell Inspiration 15", "HP Wireless Mouse", "Samsung 24-inch Monitor", "Lenovo Thinkpad E14 Laptop")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" name="Region" dataDxfId="62" dataCellStyle="Hyperlink">
+    <tableColumn id="2" name="Region" dataDxfId="85" dataCellStyle="Hyperlink">
       <calculatedColumnFormula>CHOOSE(RANDBETWEEN(1, 4), "East", "West", "North", "South")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="Sales Amount" dataDxfId="61"/>
-    <tableColumn id="4" name="Salesperson" dataDxfId="60"/>
+    <tableColumn id="3" name="Sales Amount" dataDxfId="84"/>
+    <tableColumn id="4" name="Salesperson" dataDxfId="83"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:F21" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55" headerRowCellStyle="Heading 1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:F21" totalsRowShown="0" headerRowDxfId="82" dataDxfId="80" headerRowBorderDxfId="81" tableBorderDxfId="79" totalsRowBorderDxfId="78" headerRowCellStyle="Heading 1">
   <autoFilter ref="A1:F21"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Roll No" dataDxfId="54"/>
-    <tableColumn id="2" name="Student Name" dataDxfId="53"/>
-    <tableColumn id="3" name="Maths" dataDxfId="52"/>
-    <tableColumn id="4" name="Science" dataDxfId="51"/>
-    <tableColumn id="5" name="English" dataDxfId="50"/>
-    <tableColumn id="6" name="Percentage" dataDxfId="49"/>
+    <tableColumn id="1" name="Roll No" dataDxfId="77"/>
+    <tableColumn id="2" name="Student Name" dataDxfId="76"/>
+    <tableColumn id="3" name="Maths" dataDxfId="75"/>
+    <tableColumn id="4" name="Science" dataDxfId="74"/>
+    <tableColumn id="5" name="English" dataDxfId="73"/>
+    <tableColumn id="6" name="Percentage" dataDxfId="72"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:C26" totalsRowShown="0" headerRowDxfId="48" headerRowBorderDxfId="47" tableBorderDxfId="46" totalsRowBorderDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:C26" totalsRowShown="0" headerRowDxfId="71" headerRowBorderDxfId="70" tableBorderDxfId="69" totalsRowBorderDxfId="68">
   <autoFilter ref="A1:C26"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Invoice No" dataDxfId="44"/>
-    <tableColumn id="2" name="Date" dataDxfId="43"/>
-    <tableColumn id="3" name="Sales Amount" dataDxfId="42"/>
+    <tableColumn id="1" name="Invoice No" dataDxfId="67"/>
+    <tableColumn id="2" name="Date" dataDxfId="66"/>
+    <tableColumn id="3" name="Sales Amount" dataDxfId="65"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A1:C21" totalsRowShown="0" headerRowDxfId="41" headerRowBorderDxfId="40" tableBorderDxfId="39" totalsRowBorderDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A1:C21" totalsRowShown="0" headerRowDxfId="64" headerRowBorderDxfId="63" tableBorderDxfId="62" totalsRowBorderDxfId="61">
   <autoFilter ref="A1:C21"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Employee Name" dataDxfId="37"/>
-    <tableColumn id="2" name="Department" dataDxfId="36"/>
-    <tableColumn id="3" name="Salary" dataDxfId="35"/>
+    <tableColumn id="1" name="Employee Name" dataDxfId="60"/>
+    <tableColumn id="2" name="Department" dataDxfId="59"/>
+    <tableColumn id="3" name="Salary" dataDxfId="58"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium17" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table9" displayName="Table9" ref="A1:F21" totalsRowShown="0" headerRowDxfId="34" dataDxfId="32" headerRowBorderDxfId="33" tableBorderDxfId="31" totalsRowBorderDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table9" displayName="Table9" ref="A1:F21" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56" tableBorderDxfId="54" totalsRowBorderDxfId="53">
   <autoFilter ref="A1:F21"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Student Name" dataDxfId="29"/>
-    <tableColumn id="2" name="Day 1" dataDxfId="28"/>
-    <tableColumn id="3" name="Day 2" dataDxfId="27"/>
-    <tableColumn id="4" name="Day 3" dataDxfId="26"/>
-    <tableColumn id="5" name="Day 4" dataDxfId="25"/>
-    <tableColumn id="6" name="Day 5" dataDxfId="24"/>
+    <tableColumn id="1" name="Student Name" dataDxfId="52"/>
+    <tableColumn id="2" name="Day 1" dataDxfId="51"/>
+    <tableColumn id="3" name="Day 2" dataDxfId="50"/>
+    <tableColumn id="4" name="Day 3" dataDxfId="49"/>
+    <tableColumn id="5" name="Day 4" dataDxfId="48"/>
+    <tableColumn id="6" name="Day 5" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium25" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table10" displayName="Table10" ref="A1:B21" totalsRowShown="0" headerRowDxfId="23" headerRowBorderDxfId="22" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table10" displayName="Table10" ref="A1:B21" totalsRowShown="0" headerRowDxfId="46" headerRowBorderDxfId="45" tableBorderDxfId="44" totalsRowBorderDxfId="43">
   <autoFilter ref="A1:B21"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="Order ID" dataDxfId="19"/>
-    <tableColumn id="2" name="Sales Amount" dataDxfId="18"/>
+    <tableColumn id="1" name="Order ID" dataDxfId="42"/>
+    <tableColumn id="2" name="Sales Amount" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium27" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table12" displayName="Table12" ref="A1:B21" totalsRowShown="0" headerRowDxfId="14" headerRowBorderDxfId="13" tableBorderDxfId="12" totalsRowBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table12" displayName="Table12" ref="A1:B21" totalsRowShown="0" headerRowDxfId="37" headerRowBorderDxfId="36" tableBorderDxfId="35" totalsRowBorderDxfId="34">
   <autoFilter ref="A1:B21"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="Product" dataDxfId="10"/>
-    <tableColumn id="2" name="Sales Amount" dataDxfId="9"/>
+    <tableColumn id="1" name="Product" dataDxfId="33"/>
+    <tableColumn id="2" name="Sales Amount" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3173,360 +3388,360 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="9">
         <v>32000</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="10">
         <v>44573</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="17.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <v>45000</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="10">
         <v>44260</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="17.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <v>38000</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="10">
         <v>44030</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <v>52000</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="10">
         <v>43779</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>30000</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="10">
         <v>45102</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>76000</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="10">
         <v>45896</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="17.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>45000</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="10">
         <v>44141</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>69000</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="10">
         <v>43832</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="17.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <v>74000</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="10">
         <v>46008</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>53000</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="10">
         <v>44680</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="17.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <v>68500</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="10">
         <v>44080</v>
       </c>
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:6" ht="17.25">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>83000</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="10">
         <v>44758</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17.25">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <v>60000</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="10">
         <v>45447</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="17.25">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <v>42500</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="10">
         <v>44225</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="17.25">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <v>46000</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="10">
         <v>44400</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="17.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <v>67000</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="10">
         <v>43843</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="17.25">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <v>79500</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="10">
         <v>44819</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="17.25">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <v>57500</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="10">
         <v>45930</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="17.25">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <v>84500</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="10">
         <v>44915</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="17.25">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="13">
         <v>44500</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="14">
         <v>44785</v>
       </c>
     </row>
@@ -3544,127 +3759,127 @@
   <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="25"/>
+    <col min="1" max="1" width="12.7109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="35.25" thickBot="1">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:2" ht="34.5">
+      <c r="A1" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18" thickBot="1">
-      <c r="A2" s="16" t="s">
+    <row r="2" spans="1:2" ht="17.25">
+      <c r="A2" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="65">
         <v>28000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18" thickBot="1">
-      <c r="A3" s="16" t="s">
+    <row r="3" spans="1:2" ht="17.25">
+      <c r="A3" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="65">
         <v>34000</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18" thickBot="1">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:2" ht="17.25">
+      <c r="A4" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="65">
         <v>51000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18" thickBot="1">
-      <c r="A5" s="16" t="s">
+    <row r="5" spans="1:2" ht="17.25">
+      <c r="A5" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="65">
         <v>47000</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="18" thickBot="1">
-      <c r="A6" s="16" t="s">
+    <row r="6" spans="1:2" ht="17.25">
+      <c r="A6" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="65">
         <v>29000</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17.25">
       <c r="A7" s="66" t="str">
         <f ca="1">CHOOSE(RANDBETWEEN(1,5),"Rohit","Simran","Vijay","Nisha","Mohan")</f>
-        <v>Nisha</v>
+        <v>Mohan</v>
       </c>
       <c r="B7" s="67">
         <f ca="1">RANDBETWEEN(20000, 100000)</f>
-        <v>53557</v>
+        <v>34896</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17.25">
       <c r="A8" s="66" t="str">
         <f t="shared" ref="A8:A21" ca="1" si="0">CHOOSE(RANDBETWEEN(1,5),"Rohit","Simran","Vijay","Nisha","Mohan")</f>
-        <v>Rohit</v>
+        <v>Vijay</v>
       </c>
       <c r="B8" s="67">
         <f t="shared" ref="B8:B21" ca="1" si="1">RANDBETWEEN(20000, 100000)</f>
-        <v>93063</v>
+        <v>91449</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17.25">
       <c r="A9" s="66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Simran</v>
+        <v>Nisha</v>
       </c>
       <c r="B9" s="67">
         <f t="shared" ca="1" si="1"/>
-        <v>30825</v>
+        <v>37440</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17.25">
       <c r="A10" s="66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Rohit</v>
+        <v>Vijay</v>
       </c>
       <c r="B10" s="67">
         <f t="shared" ca="1" si="1"/>
-        <v>60341</v>
+        <v>76672</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17.25">
       <c r="A11" s="66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Rohit</v>
+        <v>Simran</v>
       </c>
       <c r="B11" s="67">
         <f t="shared" ca="1" si="1"/>
-        <v>65418</v>
+        <v>85804</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17.25">
       <c r="A12" s="66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Nisha</v>
+        <v>Rohit</v>
       </c>
       <c r="B12" s="67">
         <f t="shared" ca="1" si="1"/>
-        <v>65660</v>
+        <v>62492</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17.25">
       <c r="A13" s="66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Mohan</v>
+        <v>Rohit</v>
       </c>
       <c r="B13" s="67">
         <f t="shared" ca="1" si="1"/>
-        <v>89752</v>
+        <v>74277</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17.25">
@@ -3674,37 +3889,37 @@
       </c>
       <c r="B14" s="67">
         <f t="shared" ca="1" si="1"/>
-        <v>29438</v>
+        <v>66058</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17.25">
       <c r="A15" s="66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Simran</v>
+        <v>Rohit</v>
       </c>
       <c r="B15" s="67">
         <f t="shared" ca="1" si="1"/>
-        <v>27552</v>
+        <v>28034</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="17.25">
       <c r="A16" s="66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Nisha</v>
+        <v>Mohan</v>
       </c>
       <c r="B16" s="67">
         <f t="shared" ca="1" si="1"/>
-        <v>61305</v>
+        <v>75209</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17.25">
       <c r="A17" s="66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Mohan</v>
+        <v>Vijay</v>
       </c>
       <c r="B17" s="67">
         <f t="shared" ca="1" si="1"/>
-        <v>65138</v>
+        <v>51086</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17.25">
@@ -3714,27 +3929,27 @@
       </c>
       <c r="B18" s="67">
         <f t="shared" ca="1" si="1"/>
-        <v>49904</v>
+        <v>31148</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17.25">
       <c r="A19" s="66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Rohit</v>
+        <v>Nisha</v>
       </c>
       <c r="B19" s="67">
         <f t="shared" ca="1" si="1"/>
-        <v>28402</v>
+        <v>47413</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17.25">
       <c r="A20" s="66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Rohit</v>
+        <v>Mohan</v>
       </c>
       <c r="B20" s="67">
         <f t="shared" ca="1" si="1"/>
-        <v>86188</v>
+        <v>40273</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17.25">
@@ -3744,30 +3959,36 @@
       </c>
       <c r="B21" s="67">
         <f t="shared" ca="1" si="1"/>
-        <v>67561</v>
+        <v>49225</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B21">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="greaterThan">
       <formula>5000</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="lessThan">
       <formula>3000</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="greaterThan">
       <formula>50000</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="lessThan">
       <formula>30000</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="between">
       <formula>30000</formula>
       <formula>49999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="between">
       <formula>30000</formula>
       <formula>49999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThanOrEqual">
+      <formula>50000</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="lessThan">
+      <formula>30000</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3779,7 +4000,7 @@
   <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="22.85546875" style="3" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
@@ -3787,304 +4008,304 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.75" thickBot="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
     </row>
     <row r="2" spans="1:4" ht="18" thickTop="1">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="16" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="34.5">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <v>45000</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="17.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="9">
         <v>1200</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="34.5">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="9">
         <v>18000</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="34.5">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <v>62000</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="17.25">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="20">
         <v>71000</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="21" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="17.25">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="20">
         <v>49000</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="21" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="34.5">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="20">
         <v>76000</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="21" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="34.5">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="20">
         <v>83000</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="21" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="34.5">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="20">
         <v>58000</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="21" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="34.5">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="20">
         <v>16000</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="21" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="17.25">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="20">
         <v>78000</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="21" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="34.5">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="20">
         <v>24000</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="21" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="34.5">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="20">
         <v>70000</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="21" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="34.5">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="20">
         <v>66000</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="D16" s="21" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="17.25">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="20">
         <v>48000</v>
       </c>
-      <c r="D17" s="23" t="s">
+      <c r="D17" s="21" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="34.5">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="20">
         <v>64000</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="D18" s="21" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="17.25">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="20">
         <v>22000</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="D19" s="21" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="34.5">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="20">
         <v>54000</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="21" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="34.5">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="20">
         <v>38000</v>
       </c>
-      <c r="D21" s="23" t="s">
+      <c r="D21" s="21" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="20">
         <v>93000</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="D22" s="21" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4113,426 +4334,426 @@
     <col min="3" max="3" width="10.7109375" customWidth="1"/>
     <col min="4" max="4" width="12.140625" customWidth="1"/>
     <col min="5" max="5" width="11.42578125" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" style="27" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" style="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25" thickBot="1">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="27" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="18" thickTop="1">
-      <c r="A2" s="19">
+      <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="17">
         <v>78</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="17">
         <v>82</v>
       </c>
-      <c r="E2" s="19">
+      <c r="E2" s="17">
         <v>74</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="24">
         <v>0.78</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="17.25">
-      <c r="A3" s="19">
+      <c r="A3" s="17">
         <v>2</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="17">
         <v>65</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="17">
         <v>70</v>
       </c>
-      <c r="E3" s="19">
+      <c r="E3" s="17">
         <v>68</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="24">
         <v>0.67666666666666664</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="17.25">
-      <c r="A4" s="19">
+      <c r="A4" s="17">
         <v>3</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="17">
         <v>90</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="17">
         <v>88</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="17">
         <v>92</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="24">
         <v>0.9</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17.25">
-      <c r="A5" s="19">
+      <c r="A5" s="17">
         <v>4</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="17">
         <v>35</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="17">
         <v>40</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="17">
         <v>38</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="24">
         <v>0.37666666666666665</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17.25">
-      <c r="A6" s="19">
+      <c r="A6" s="17">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="17">
         <v>55</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="17">
         <v>60</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="17">
         <v>58</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="24">
         <v>0.57666666666666666</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17.25">
-      <c r="A7" s="19">
+      <c r="A7" s="17">
         <v>6</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="21">
         <v>51</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="21">
         <v>48</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="21">
         <v>73</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="24">
         <v>0.57333333333333336</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="17.25">
-      <c r="A8" s="19">
+      <c r="A8" s="17">
         <v>7</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="21">
         <v>79</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="21">
         <v>76</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="21">
         <v>60</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="24">
         <v>0.71666666666666667</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17.25">
-      <c r="A9" s="19">
+      <c r="A9" s="17">
         <v>8</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="21">
         <v>89</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="21">
         <v>85</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="21">
         <v>92</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="24">
         <v>0.88666666666666671</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="17.25">
-      <c r="A10" s="19">
+      <c r="A10" s="17">
         <v>9</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="21">
         <v>37</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="21">
         <v>51</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="21">
         <v>44</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="24">
         <v>0.44</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17.25">
-      <c r="A11" s="19">
+      <c r="A11" s="17">
         <v>10</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="21">
         <v>44</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="21">
         <v>100</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="21">
         <v>99</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="24">
         <v>0.81</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="17.25">
-      <c r="A12" s="19">
+      <c r="A12" s="17">
         <v>11</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="21">
         <v>43</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="21">
         <v>25</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="21">
         <v>57</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="24">
         <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17.25">
-      <c r="A13" s="19">
+      <c r="A13" s="17">
         <v>12</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="21">
         <v>97</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="21">
         <v>61</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="21">
         <v>56</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="24">
         <v>0.71333333333333337</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17.25">
-      <c r="A14" s="19">
+      <c r="A14" s="17">
         <v>13</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="21">
         <v>50</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="21">
         <v>84</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="21">
         <v>26</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="24">
         <v>0.53333333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="17.25">
-      <c r="A15" s="19">
+      <c r="A15" s="17">
         <v>14</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="21">
         <v>68</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="21">
         <v>39</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="21">
         <v>26</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="24">
         <v>0.44333333333333336</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="17.25">
-      <c r="A16" s="19">
+      <c r="A16" s="17">
         <v>15</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="21">
         <v>79</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="21">
         <v>35</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="21">
         <v>100</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="24">
         <v>0.71333333333333337</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="17.25">
-      <c r="A17" s="19">
+      <c r="A17" s="17">
         <v>16</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="23">
+      <c r="C17" s="21">
         <v>98</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="21">
         <v>62</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="21">
         <v>69</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="24">
         <v>0.76333333333333331</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17.25">
-      <c r="A18" s="19">
+      <c r="A18" s="17">
         <v>17</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="23">
+      <c r="C18" s="21">
         <v>28</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="21">
         <v>58</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="21">
         <v>45</v>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="24">
         <v>0.43666666666666665</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="17.25">
-      <c r="A19" s="19">
+      <c r="A19" s="17">
         <v>18</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="23">
+      <c r="C19" s="21">
         <v>24</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="21">
         <v>68</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="21">
         <v>80</v>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="24">
         <v>0.57333333333333336</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="17.25">
-      <c r="A20" s="19">
+      <c r="A20" s="17">
         <v>19</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="23">
+      <c r="C20" s="21">
         <v>17</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="21">
         <v>68</v>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="21">
         <v>72</v>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="24">
         <v>0.52333333333333332</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="17.25">
-      <c r="A21" s="30">
+      <c r="A21" s="28">
         <v>20</v>
       </c>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="29">
         <v>48</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="29">
         <v>60</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="29">
         <v>86</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="30">
         <v>0.64666666666666661</v>
       </c>
     </row>
@@ -4550,282 +4771,282 @@
   <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="25" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="25"/>
+    <col min="1" max="1" width="19.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="23" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="37" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="33">
+      <c r="B2" s="31">
         <v>45292</v>
       </c>
-      <c r="C2" s="35">
+      <c r="C2" s="33">
         <v>12000</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="33">
+      <c r="B3" s="31">
         <v>45294</v>
       </c>
-      <c r="C3" s="35">
+      <c r="C3" s="33">
         <v>25000</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B4" s="33">
+      <c r="B4" s="31">
         <v>45296</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="33">
         <v>8000</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="31">
         <v>45299</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="33">
         <v>32000</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="31">
         <v>45301</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="33">
         <v>15000</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="32">
         <v>45999</v>
       </c>
-      <c r="C7" s="36">
+      <c r="C7" s="34">
         <v>16000</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="32">
         <v>46183</v>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="34">
         <v>6000</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="17.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="32">
         <v>45671</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="34">
         <v>12000</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="32">
         <v>45997</v>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="34">
         <v>14000</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B11" s="34">
+      <c r="B11" s="32">
         <v>46066</v>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="34">
         <v>11000</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B12" s="34">
+      <c r="B12" s="32">
         <v>45406</v>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="34">
         <v>45000</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="17.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="32">
         <v>45954</v>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="34">
         <v>43000</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="17.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B14" s="34">
+      <c r="B14" s="32">
         <v>45309</v>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="34">
         <v>5000</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="17.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="32">
         <v>45723</v>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="34">
         <v>41000</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="17.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B16" s="34">
+      <c r="B16" s="32">
         <v>45868</v>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="34">
         <v>45000</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="17.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B17" s="34">
+      <c r="B17" s="32">
         <v>45891</v>
       </c>
-      <c r="C17" s="36">
+      <c r="C17" s="34">
         <v>23000</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="17.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B18" s="34">
+      <c r="B18" s="32">
         <v>46089</v>
       </c>
-      <c r="C18" s="36">
+      <c r="C18" s="34">
         <v>24000</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B19" s="34">
+      <c r="B19" s="32">
         <v>45904</v>
       </c>
-      <c r="C19" s="36">
+      <c r="C19" s="34">
         <v>44000</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="17.25">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B20" s="34">
+      <c r="B20" s="32">
         <v>45786</v>
       </c>
-      <c r="C20" s="36">
+      <c r="C20" s="34">
         <v>29000</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="17.25">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="32">
         <v>45435</v>
       </c>
-      <c r="C21" s="36">
+      <c r="C21" s="34">
         <v>5000</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="17.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="36"/>
+      <c r="A22" s="2"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="34"/>
     </row>
     <row r="23" spans="1:3" ht="17.25">
-      <c r="A23" s="41" t="s">
+      <c r="A23" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="B23" s="34"/>
-      <c r="C23" s="42">
+      <c r="B23" s="32"/>
+      <c r="C23" s="40">
         <v>455000</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="17.25">
-      <c r="A24" s="41" t="s">
+      <c r="A24" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="B24" s="34"/>
-      <c r="C24" s="42">
+      <c r="B24" s="32"/>
+      <c r="C24" s="40">
         <v>22750</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="17.25">
-      <c r="A25" s="41" t="s">
+      <c r="A25" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="B25" s="34"/>
-      <c r="C25" s="42">
+      <c r="B25" s="32"/>
+      <c r="C25" s="40">
         <v>45000</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="17.25">
-      <c r="A26" s="43" t="s">
+      <c r="A26" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="B26" s="40"/>
-      <c r="C26" s="44">
+      <c r="B26" s="38"/>
+      <c r="C26" s="42">
         <v>5000</v>
       </c>
     </row>
@@ -4842,285 +5063,285 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22" style="25" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" style="25" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="25" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="25"/>
-    <col min="5" max="5" width="13" style="25" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35" style="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="25"/>
+    <col min="1" max="1" width="22" style="23" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="23" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="23"/>
+    <col min="5" max="5" width="13" style="23" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="37" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="33.75" customHeight="1">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="35">
+      <c r="C2" s="33">
         <v>28000</v>
       </c>
-      <c r="G2" s="48" t="s">
+      <c r="G2" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="H2" s="48" t="s">
+      <c r="H2" s="46" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="17.25">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="35">
+      <c r="C3" s="33">
         <v>45000</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="20.25">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="33">
         <v>50000</v>
       </c>
-      <c r="F4" s="49" t="s">
+      <c r="F4" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="49">
+      <c r="G4" s="47">
         <v>429000</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="15">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="20.25">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="33">
         <v>42000</v>
       </c>
-      <c r="F5" s="49" t="s">
+      <c r="F5" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="49">
+      <c r="G5" s="47">
         <v>318000</v>
       </c>
-      <c r="H5" s="50">
+      <c r="H5" s="48">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="20.25">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="33">
         <v>30000</v>
       </c>
-      <c r="F6" s="49" t="s">
+      <c r="F6" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="49">
+      <c r="G6" s="47">
         <v>355000</v>
       </c>
-      <c r="H6" s="50">
+      <c r="H6" s="48">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="17.25">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="33">
         <v>38000</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.25">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="47" t="s">
+      <c r="B8" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="55">
+      <c r="C8" s="53">
         <v>53000</v>
       </c>
-      <c r="F8" s="49" t="s">
+      <c r="F8" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="G8" s="50">
+      <c r="G8" s="48">
         <f>AVERAGE(C2:C21)</f>
         <v>55100</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="17.25">
-      <c r="A9" s="54" t="s">
+      <c r="A9" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="55">
+      <c r="C9" s="53">
         <v>49000</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="17.25">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="55">
+      <c r="C10" s="53">
         <v>43000</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="17.25">
-      <c r="A11" s="54" t="s">
+      <c r="A11" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="55">
+      <c r="C11" s="53">
         <v>76000</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="17.25">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="B12" s="47" t="s">
+      <c r="B12" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="55">
+      <c r="C12" s="53">
         <v>33000</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="17.25">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="47" t="s">
+      <c r="B13" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="55">
+      <c r="C13" s="53">
         <v>87000</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="17.25">
-      <c r="A14" s="54" t="s">
+      <c r="A14" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="47" t="s">
+      <c r="B14" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="55">
+      <c r="C14" s="53">
         <v>43000</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="17.25">
-      <c r="A15" s="54" t="s">
+      <c r="A15" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="55">
+      <c r="C15" s="53">
         <v>41000</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="17.25">
-      <c r="A16" s="54" t="s">
+      <c r="A16" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="55">
+      <c r="C16" s="53">
         <v>88000</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="17.25">
-      <c r="A17" s="53" t="s">
+      <c r="A17" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="47" t="s">
+      <c r="B17" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="55">
+      <c r="C17" s="53">
         <v>55000</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="17.25">
-      <c r="A18" s="53" t="s">
+      <c r="A18" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="B18" s="47" t="s">
+      <c r="B18" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="55">
+      <c r="C18" s="53">
         <v>81000</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25">
-      <c r="A19" s="54" t="s">
+      <c r="A19" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="55">
+      <c r="C19" s="53">
         <v>71000</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="17.25">
-      <c r="A20" s="54" t="s">
+      <c r="A20" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="47" t="s">
+      <c r="B20" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="55">
+      <c r="C20" s="53">
         <v>51000</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="17.25">
-      <c r="A21" s="56" t="s">
+      <c r="A21" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="57" t="s">
+      <c r="B21" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="58">
+      <c r="C21" s="56">
         <v>98000</v>
       </c>
     </row>
@@ -5137,451 +5358,451 @@
   <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20" style="25" customWidth="1"/>
-    <col min="2" max="6" width="10.140625" style="25" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" style="25"/>
-    <col min="10" max="10" width="10.42578125" style="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="25"/>
+    <col min="1" max="1" width="20" style="23" customWidth="1"/>
+    <col min="2" max="6" width="10.140625" style="23" customWidth="1"/>
+    <col min="7" max="9" width="9.140625" style="23"/>
+    <col min="10" max="10" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="37" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="17.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="33" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="17.25">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="F3" s="33" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" thickBot="1">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="33" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="18" thickBot="1">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="J5" s="24" t="s">
+      <c r="J5" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="K5" s="24" t="s">
+      <c r="K5" s="22" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="18" thickBot="1">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="J6" s="24" t="s">
+      <c r="J6" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="K6" s="24">
+      <c r="K6" s="22">
         <f>COUNTIF(B2:F21,"P")</f>
         <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="18" thickBot="1">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="J7" s="24" t="s">
+      <c r="J7" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="K7" s="24">
+      <c r="K7" s="22">
         <f>COUNTIF(B2:F21,"A")</f>
         <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="17.25">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="33" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="17.25">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="33" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="17.25">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="33" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="17.25">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="33" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="17.25">
-      <c r="A12" s="59" t="s">
+      <c r="A12" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F12" s="35" t="s">
+      <c r="F12" s="33" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="17.25">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F13" s="35" t="s">
+      <c r="F13" s="33" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="17.25">
-      <c r="A14" s="59" t="s">
+      <c r="A14" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F14" s="35" t="s">
+      <c r="F14" s="33" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25">
-      <c r="A15" s="59" t="s">
+      <c r="A15" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F15" s="35" t="s">
+      <c r="F15" s="33" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="17.25">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F16" s="35" t="s">
+      <c r="F16" s="33" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="17.25">
-      <c r="A17" s="59" t="s">
+      <c r="A17" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="F17" s="35" t="s">
+      <c r="F17" s="33" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17.25">
-      <c r="A18" s="59" t="s">
+      <c r="A18" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F18" s="35" t="s">
+      <c r="F18" s="33" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="17.25">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E19" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F19" s="35" t="s">
+      <c r="F19" s="33" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="17.25">
-      <c r="A20" s="59" t="s">
+      <c r="A20" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="F20" s="35" t="s">
+      <c r="F20" s="33" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="17.25">
-      <c r="A21" s="60" t="s">
+      <c r="A21" s="58" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C21" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="E21" s="30" t="s">
+      <c r="E21" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="F21" s="61" t="s">
+      <c r="F21" s="59" t="s">
         <v>85</v>
       </c>
     </row>
@@ -5598,194 +5819,194 @@
   <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="51" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" style="51" customWidth="1"/>
-    <col min="3" max="4" width="9.140625" style="25"/>
-    <col min="5" max="5" width="15.7109375" style="25" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="25"/>
+    <col min="1" max="1" width="13.5703125" style="49" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" style="49" customWidth="1"/>
+    <col min="3" max="4" width="9.140625" style="23"/>
+    <col min="5" max="5" width="15.7109375" style="23" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="37" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="35">
+      <c r="B2" s="33">
         <v>4500</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="17.25">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="35">
+      <c r="B3" s="33">
         <v>12000</v>
       </c>
-      <c r="E3" s="45" t="s">
+      <c r="E3" s="43" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="17.25">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="35">
+      <c r="B4" s="33">
         <v>8000</v>
       </c>
-      <c r="E4" s="45" t="s">
+      <c r="E4" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="F4" s="50">
+      <c r="F4" s="48">
         <v>496000</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17.25">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="35">
+      <c r="B5" s="33">
         <v>25000</v>
       </c>
-      <c r="E5" s="45" t="s">
+      <c r="E5" s="43" t="s">
         <v>150</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="15">
         <v>15300</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17.25">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="51" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="33">
         <v>3000</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17.25">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="33">
         <v>15000</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="17.25">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="51" t="s">
         <v>135</v>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="33">
         <v>6000</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17.25">
-      <c r="A9" s="53" t="s">
+      <c r="A9" s="51" t="s">
         <v>136</v>
       </c>
-      <c r="B9" s="62">
+      <c r="B9" s="60">
         <v>9000</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="17.25">
-      <c r="A10" s="53" t="s">
+      <c r="A10" s="51" t="s">
         <v>137</v>
       </c>
-      <c r="B10" s="62">
+      <c r="B10" s="60">
         <v>25000</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17.25">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="51" t="s">
         <v>138</v>
       </c>
-      <c r="B11" s="62">
+      <c r="B11" s="60">
         <v>50000</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="17.25">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="51" t="s">
         <v>139</v>
       </c>
-      <c r="B12" s="62">
+      <c r="B12" s="60">
         <v>45000</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17.25">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="51" t="s">
         <v>140</v>
       </c>
-      <c r="B13" s="62">
+      <c r="B13" s="60">
         <v>79000</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17.25">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="51" t="s">
         <v>141</v>
       </c>
-      <c r="B14" s="62">
+      <c r="B14" s="60">
         <v>4000</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="17.25">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="51" t="s">
         <v>142</v>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="33">
         <v>9000</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="17.25">
-      <c r="A16" s="53" t="s">
+      <c r="A16" s="51" t="s">
         <v>143</v>
       </c>
-      <c r="B16" s="62">
+      <c r="B16" s="60">
         <v>3800</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17.25">
-      <c r="A17" s="53" t="s">
+      <c r="A17" s="51" t="s">
         <v>144</v>
       </c>
-      <c r="B17" s="35">
+      <c r="B17" s="33">
         <v>66000</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17.25">
-      <c r="A18" s="53" t="s">
+      <c r="A18" s="51" t="s">
         <v>145</v>
       </c>
-      <c r="B18" s="35">
+      <c r="B18" s="33">
         <v>71000</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17.25">
-      <c r="A19" s="53" t="s">
+      <c r="A19" s="51" t="s">
         <v>146</v>
       </c>
-      <c r="B19" s="35">
+      <c r="B19" s="33">
         <v>7500</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17.25">
-      <c r="A20" s="53" t="s">
+      <c r="A20" s="51" t="s">
         <v>147</v>
       </c>
-      <c r="B20" s="35">
+      <c r="B20" s="33">
         <v>23000</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17.25">
-      <c r="A21" s="63" t="s">
+      <c r="A21" s="61" t="s">
         <v>148</v>
       </c>
-      <c r="B21" s="61">
+      <c r="B21" s="59">
         <v>85000</v>
       </c>
     </row>
@@ -5802,190 +6023,190 @@
   <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" style="52" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" style="25" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="25"/>
+    <col min="1" max="1" width="14.28515625" style="50" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" style="23" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="37" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="35">
+      <c r="B2" s="33">
         <v>22000</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17.25">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="35">
+      <c r="B3" s="33">
         <v>3500</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17.25">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="B4" s="35">
+      <c r="B4" s="33">
         <v>58000</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="17.25">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="35">
+      <c r="B5" s="33">
         <v>1800</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="17.25">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="33">
         <v>12000</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17.25">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="62" t="s">
         <v>98</v>
       </c>
-      <c r="B7" s="55">
+      <c r="B7" s="53">
         <v>50000</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17.25">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="55">
+      <c r="B8" s="53">
         <v>76000</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17.25">
-      <c r="A9" s="64" t="s">
+      <c r="A9" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="55">
+      <c r="B9" s="53">
         <v>9800</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17.25">
-      <c r="A10" s="64" t="s">
+      <c r="A10" s="62" t="s">
         <v>95</v>
       </c>
-      <c r="B10" s="55">
+      <c r="B10" s="53">
         <v>25000</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17.25">
-      <c r="A11" s="64" t="s">
+      <c r="A11" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="B11" s="55">
+      <c r="B11" s="53">
         <v>4000</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17.25">
-      <c r="A12" s="64" t="s">
+      <c r="A12" s="62" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="55">
+      <c r="B12" s="53">
         <v>92000</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17.25">
-      <c r="A13" s="64" t="s">
+      <c r="A13" s="62" t="s">
         <v>95</v>
       </c>
-      <c r="B13" s="55">
+      <c r="B13" s="53">
         <v>6700</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17.25">
-      <c r="A14" s="64" t="s">
+      <c r="A14" s="62" t="s">
         <v>98</v>
       </c>
-      <c r="B14" s="55">
+      <c r="B14" s="53">
         <v>89000</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17.25">
-      <c r="A15" s="64" t="s">
+      <c r="A15" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="B15" s="55">
+      <c r="B15" s="53">
         <v>99000</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="17.25">
-      <c r="A16" s="64" t="s">
+      <c r="A16" s="62" t="s">
         <v>95</v>
       </c>
-      <c r="B16" s="55">
+      <c r="B16" s="53">
         <v>61000</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17.25">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="62" t="s">
         <v>95</v>
       </c>
-      <c r="B17" s="55">
+      <c r="B17" s="53">
         <v>10000</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17.25">
-      <c r="A18" s="64" t="s">
+      <c r="A18" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="55">
+      <c r="B18" s="53">
         <v>45000</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17.25">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="62" t="s">
         <v>98</v>
       </c>
-      <c r="B19" s="55">
+      <c r="B19" s="53">
         <v>3200</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17.25">
-      <c r="A20" s="64" t="s">
+      <c r="A20" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="55">
+      <c r="B20" s="53">
         <v>56000</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17.25">
-      <c r="A21" s="65" t="s">
+      <c r="A21" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="58">
+      <c r="B21" s="56">
         <v>79000</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D4">
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="3" operator="greaterThan">
       <formula>20000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B21">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="1" operator="lessThan">
       <formula>5000</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="2" operator="greaterThan">
       <formula>20000</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6001,257 +6222,256 @@
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="12.28515625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10" style="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="12.28515625" style="25"/>
+    <col min="1" max="1" width="10" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="12.28515625" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="16" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.25">
-      <c r="A2" s="19">
+      <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="17">
         <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.25">
-      <c r="A3" s="19">
+      <c r="A3" s="17">
         <v>2</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="17">
         <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.25">
-      <c r="A4" s="19">
+      <c r="A4" s="17">
         <v>3</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="17">
         <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.25">
-      <c r="A5" s="19">
+      <c r="A5" s="17">
         <v>4</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="17">
         <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.25">
-      <c r="A6" s="19">
+      <c r="A6" s="17">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="17">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.25">
-      <c r="A7" s="19">
+      <c r="A7" s="17">
         <v>6</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="46">
+      <c r="C7" s="44">
         <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.25">
-      <c r="A8" s="19">
+      <c r="A8" s="17">
         <v>7</v>
       </c>
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="46">
+      <c r="C8" s="44">
         <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="17.25">
-      <c r="A9" s="19">
+      <c r="A9" s="17">
         <v>8</v>
       </c>
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="46">
+      <c r="C9" s="44">
         <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17.25">
-      <c r="A10" s="19">
+      <c r="A10" s="17">
         <v>9</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C10" s="46">
+      <c r="C10" s="44">
         <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17.25">
-      <c r="A11" s="19">
+      <c r="A11" s="17">
         <v>10</v>
       </c>
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="C11" s="46">
+      <c r="C11" s="44">
         <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17.25">
-      <c r="A12" s="19">
+      <c r="A12" s="17">
         <v>11</v>
       </c>
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="C12" s="46">
+      <c r="C12" s="44">
         <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="17.25">
-      <c r="A13" s="19">
+      <c r="A13" s="17">
         <v>12</v>
       </c>
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="C13" s="46">
+      <c r="C13" s="44">
         <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="17.25">
-      <c r="A14" s="19">
+      <c r="A14" s="17">
         <v>13</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="46">
+      <c r="C14" s="44">
         <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="17.25">
-      <c r="A15" s="19">
+      <c r="A15" s="17">
         <v>14</v>
       </c>
-      <c r="B15" s="46" t="s">
+      <c r="B15" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="46">
+      <c r="C15" s="44">
         <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="17.25">
-      <c r="A16" s="19">
+      <c r="A16" s="17">
         <v>15</v>
       </c>
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="46">
+      <c r="C16" s="44">
         <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="17.25">
-      <c r="A17" s="19">
+      <c r="A17" s="17">
         <v>16</v>
       </c>
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="46">
+      <c r="C17" s="44">
         <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="17.25">
-      <c r="A18" s="19">
+      <c r="A18" s="17">
         <v>17</v>
       </c>
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="46">
+      <c r="C18" s="44">
         <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25">
-      <c r="A19" s="19">
+      <c r="A19" s="17">
         <v>18</v>
       </c>
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="46">
+      <c r="C19" s="44">
         <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="17.25">
-      <c r="A20" s="19">
+      <c r="A20" s="17">
         <v>19</v>
       </c>
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="C20" s="46">
+      <c r="C20" s="44">
         <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="17.25">
-      <c r="A21" s="19">
+      <c r="A21" s="17">
         <v>20</v>
       </c>
-      <c r="B21" s="46" t="s">
+      <c r="B21" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="C21" s="46">
+      <c r="C21" s="44">
         <v>70</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="lessThan">
-      <formula>"4$C$2:$C$21"</formula>
+  <conditionalFormatting sqref="C2:C21">
+    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual">
+      <formula>75</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C21">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="greaterThanOrEqual">
+      <formula>75</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
       <formula>40</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="greaterThan">
-      <formula>75</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>